--- a/ig/DM-JUILLET-2026/ValueSet-JDV-J34-CategorieOrganisation-ROR.xlsx
+++ b/ig/DM-JUILLET-2026/ValueSet-JDV-J34-CategorieOrganisation-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="629">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="645" uniqueCount="643">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260629120000</t>
+    <t>20260730120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:00:00+01:00</t>
+    <t>2026-07-30T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1890,7 +1890,49 @@
     <t>313</t>
   </si>
   <si>
-    <t>Antennes des urgences</t>
+    <t>Antenne des urgences</t>
+  </si>
+  <si>
+    <t>314</t>
+  </si>
+  <si>
+    <t>Centre de Prise en Charge des Auteurs et/ou Auteures de violences conjugales (CPCA)</t>
+  </si>
+  <si>
+    <t>315</t>
+  </si>
+  <si>
+    <t>Equipe de Soins Spécialisés (ESS)</t>
+  </si>
+  <si>
+    <t>316</t>
+  </si>
+  <si>
+    <t>Société de téléconsultation</t>
+  </si>
+  <si>
+    <t>317</t>
+  </si>
+  <si>
+    <t>Unité hospitalière de soins de support</t>
+  </si>
+  <si>
+    <t>318</t>
+  </si>
+  <si>
+    <t>Groupe plaies et cicatrisation (dont équipe mobile)</t>
+  </si>
+  <si>
+    <t>319</t>
+  </si>
+  <si>
+    <t>Centre du sommeil</t>
+  </si>
+  <si>
+    <t>320</t>
+  </si>
+  <si>
+    <t>Structure de relayage au domicile</t>
   </si>
   <si>
     <t/>
@@ -2161,7 +2203,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B302"/>
+  <dimension ref="A1:B309"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -4573,15 +4615,71 @@
         <v>626</v>
       </c>
       <c r="B301" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B302" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="B303" t="s" s="2">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="B304" t="s" s="2">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="B305" t="s" s="2">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="B306" t="s" s="2">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="B307" t="s" s="2">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="B308" t="s" s="2">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="B309" t="s" s="2">
+        <v>642</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM-JUILLET-2026/ValueSet-JDV-J34-CategorieOrganisation-ROR.xlsx
+++ b/ig/DM-JUILLET-2026/ValueSet-JDV-J34-CategorieOrganisation-ROR.xlsx
@@ -1932,7 +1932,7 @@
     <t>320</t>
   </si>
   <si>
-    <t>Structure de relayage au domicile</t>
+    <t>Offre de relayage au domicile</t>
   </si>
   <si>
     <t/>
